--- a/job_application_forms/002_flight_attendant_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/002_flight_attendant_job_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,8 +788,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,12 +817,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high_school_diploma',_'value':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High School Diploma', 'value': 'High School Diploma'}</t>
+          <t>High School Diploma</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'college_diploma',_'value':_'college_diploma'}</t>
+          <t>college_diploma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'College Diploma', 'value': 'College Diploma'}</t>
+          <t>College Diploma</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'flight_attendant_experience',_'value':_'flight_attendant_experience'}</t>
+          <t>flight_attendant_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Flight Attendant Experience', 'value': 'Flight Attendant Experience'}</t>
+          <t>Flight Attendant Experience</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Full-Time', 'value': 'Full-Time'}</t>
+          <t>Full-Time</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Part-Time', 'value': 'Part-Time'}</t>
+          <t>Part-Time</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'id',_'value':_'id'}</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'ID', 'value': 'ID'}</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'passport',_'value':_'passport'}</t>
+          <t>passport</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Passport', 'value': 'Passport'}</t>
+          <t>Passport</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_"driver's_license",_'value':_"driver's_license"}</t>
+          <t>driver's_license</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': "Driver's License", 'value': "Driver's License"}</t>
+          <t>Driver's License</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'reference_1',_'value':_'reference_1'}</t>
+          <t>reference_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Reference 1', 'value': 'Reference 1'}</t>
+          <t>Reference 1</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'reference_2',_'value':_'reference_2'}</t>
+          <t>reference_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Reference 2', 'value': 'Reference 2'}</t>
+          <t>Reference 2</t>
         </is>
       </c>
     </row>
